--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9329,0.0421,0.0154,0.0011</t>
-  </si>
-  <si>
-    <t>0.9421,0.0194,0.0110,0.0070</t>
-  </si>
-  <si>
-    <t>0.9402,0.0505,0.0052,0.0007</t>
-  </si>
-  <si>
-    <t>0.9313,0.0569,0.0024,0.0009</t>
-  </si>
-  <si>
-    <t>0.8619,0.1261,0.0025,0.0018</t>
-  </si>
-  <si>
-    <t>0.9171,0.0742,0.0033,0.0015</t>
-  </si>
-  <si>
-    <t>0.9662,0.0295,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.6731,0.3771,0.0070,0.0014</t>
-  </si>
-  <si>
-    <t>0.9387,0.0661,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.9458,0.0630,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.7848,0.2475,0.0153,0.0022</t>
-  </si>
-  <si>
-    <t>0.9543,0.0340,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9902,0.0023,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.8885,0.0244,0.1030,0.0027</t>
-  </si>
-  <si>
-    <t>0.9567,0.0154,0.0180,0.0004</t>
-  </si>
-  <si>
-    <t>0.9555,0.0144,0.0177,0.0003</t>
-  </si>
-  <si>
-    <t>0.9664,0.0210,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.5779,0.5900,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.8934,0.1628,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.7220,0.3902,0.0070,0.0005</t>
-  </si>
-  <si>
-    <t>0.8392,0.2621,0.0041,0.0004</t>
-  </si>
-  <si>
-    <t>0.0961,0.9557,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9827,0.0040,0.0111,0.0002</t>
-  </si>
-  <si>
-    <t>0.9732,0.0017,0.0415,0.0003</t>
-  </si>
-  <si>
-    <t>0.9585,0.0051,0.0554,0.0005</t>
-  </si>
-  <si>
-    <t>0.9493,0.0039,0.0805,0.0003</t>
-  </si>
-  <si>
-    <t>0.7972,0.0101,0.3600,0.0026</t>
-  </si>
-  <si>
-    <t>0.9706,0.0029,0.0391,0.0003</t>
-  </si>
-  <si>
-    <t>0.8911,0.0015,0.2544,0.0002</t>
-  </si>
-  <si>
-    <t>0.4910,0.6904,0.0039,0.0006</t>
-  </si>
-  <si>
-    <t>0.9699,0.0166,0.0051,0.0008</t>
-  </si>
-  <si>
-    <t>0.0102,0.0416,0.9857,0.0013</t>
-  </si>
-  <si>
-    <t>0.9727,0.0154,0.0050,0.0003</t>
-  </si>
-  <si>
-    <t>0.9732,0.0202,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9238,0.0495,0.0159,0.0012</t>
-  </si>
-  <si>
-    <t>0.8620,0.2116,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9550,0.0535,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.2374,0.3652,0.1469,0.0004</t>
-  </si>
-  <si>
-    <t>0.9738,0.0002,0.0809,0.0001</t>
-  </si>
-  <si>
-    <t>0.9619,0.0037,0.0367,0.0002</t>
-  </si>
-  <si>
-    <t>0.9605,0.0011,0.0519,0.0015</t>
-  </si>
-  <si>
-    <t>0.7522,0.0127,0.3160,0.0002</t>
-  </si>
-  <si>
-    <t>0.8173,0.0802,0.0192,0.0001</t>
-  </si>
-  <si>
-    <t>0.9844,0.0022,0.0195,0.0003</t>
-  </si>
-  <si>
-    <t>0.9174,0.0442,0.0143,0.0042</t>
-  </si>
-  <si>
-    <t>0.9665,0.0263,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.8624,0.1597,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.8653,0.1316,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.0982,0.0108,0.9404,0.0009</t>
-  </si>
-  <si>
-    <t>0.3665,0.0196,0.7456,0.0010</t>
-  </si>
-  <si>
-    <t>0.8378,0.0139,0.2209,0.0015</t>
-  </si>
-  <si>
-    <t>0.8886,0.0097,0.1905,0.0014</t>
-  </si>
-  <si>
-    <t>0.0471,0.0135,0.9683,0.0004</t>
-  </si>
-  <si>
-    <t>0.8995,0.0200,0.0773,0.0005</t>
-  </si>
-  <si>
-    <t>0.9358,0.0424,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.6743,0.3769,0.0097,0.0017</t>
-  </si>
-  <si>
-    <t>0.7963,0.2052,0.0095,0.0032</t>
-  </si>
-  <si>
-    <t>0.0498,0.1952,0.9378,0.0100</t>
-  </si>
-  <si>
-    <t>0.9751,0.0199,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.8665,0.1357,0.0054,0.0015</t>
-  </si>
-  <si>
-    <t>0.9422,0.0409,0.0015,0.0013</t>
-  </si>
-  <si>
-    <t>0.0364,0.9383,0.2543,0.0008</t>
-  </si>
-  <si>
-    <t>0.1542,0.0033,0.9415,0.0001</t>
-  </si>
-  <si>
-    <t>0.7757,0.0071,0.3818,0.0016</t>
-  </si>
-  <si>
-    <t>0.7907,0.0133,0.1726,0.0002</t>
-  </si>
-  <si>
-    <t>0.6024,0.0164,0.5396,0.0007</t>
-  </si>
-  <si>
-    <t>0.8874,0.1131,0.0151,0.0003</t>
-  </si>
-  <si>
-    <t>0.1166,0.9445,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9192,0.0794,0.0107,0.0005</t>
-  </si>
-  <si>
-    <t>0.8336,0.2626,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0463,0.8130,0.2355,0.0005</t>
-  </si>
-  <si>
-    <t>0.7072,0.0714,0.1780,0.0008</t>
-  </si>
-  <si>
-    <t>0.9294,0.0115,0.0868,0.0005</t>
-  </si>
-  <si>
-    <t>0.0973,0.8365,0.1158,0.0004</t>
-  </si>
-  <si>
-    <t>0.5085,0.0538,0.3488,0.0005</t>
-  </si>
-  <si>
-    <t>0.9687,0.0054,0.0071,0.0046</t>
-  </si>
-  <si>
-    <t>0.9080,0.0403,0.0114,0.0105</t>
-  </si>
-  <si>
-    <t>0.9778,0.0046,0.0040,0.0018</t>
-  </si>
-  <si>
-    <t>0.9158,0.0589,0.0058,0.0037</t>
-  </si>
-  <si>
-    <t>0.8832,0.1081,0.0075,0.0031</t>
-  </si>
-  <si>
-    <t>0.9393,0.0208,0.0080,0.0073</t>
-  </si>
-  <si>
-    <t>0.2415,0.1836,0.6322,0.0025</t>
-  </si>
-  <si>
-    <t>0.5509,0.0335,0.4371,0.0007</t>
-  </si>
-  <si>
-    <t>0.9276,0.0059,0.0892,0.0002</t>
-  </si>
-  <si>
-    <t>0.8935,0.0041,0.2305,0.0008</t>
-  </si>
-  <si>
-    <t>0.6276,0.0269,0.3836,0.0003</t>
-  </si>
-  <si>
-    <t>0.7446,0.1007,0.0197,0.0000</t>
-  </si>
-  <si>
-    <t>0.8160,0.1761,0.0046,0.0022</t>
-  </si>
-  <si>
-    <t>0.7229,0.3740,0.0075,0.0012</t>
-  </si>
-  <si>
-    <t>0.8618,0.1657,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9681,0.0347,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.7505,0.2038,0.0030,0.0026</t>
-  </si>
-  <si>
-    <t>0.8585,0.1483,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.9065,0.1399,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.8960,0.1376,0.0028,0.0007</t>
-  </si>
-  <si>
-    <t>0.6789,0.3616,0.0030,0.0016</t>
-  </si>
-  <si>
-    <t>0.7970,0.2306,0.0032,0.0014</t>
-  </si>
-  <si>
-    <t>0.9411,0.0818,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.9692,0.0246,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.8779,0.1232,0.0014,0.0009</t>
-  </si>
-  <si>
-    <t>0.8398,0.2126,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.8997,0.0851,0.0068,0.0015</t>
-  </si>
-  <si>
-    <t>0.9202,0.0784,0.0021,0.0018</t>
-  </si>
-  <si>
-    <t>0.0355,0.0314,0.9682,0.0005</t>
-  </si>
-  <si>
-    <t>0.8698,0.0275,0.0966,0.0005</t>
-  </si>
-  <si>
-    <t>0.9648,0.0077,0.0267,0.0003</t>
-  </si>
-  <si>
-    <t>0.9619,0.0026,0.0571,0.0005</t>
-  </si>
-  <si>
-    <t>0.4032,0.7592,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.3463,0.7840,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.6715,0.4594,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.8424,0.2430,0.0055,0.0003</t>
-  </si>
-  <si>
-    <t>0.5522,0.5850,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.1212,0.9145,0.0084,0.0003</t>
-  </si>
-  <si>
-    <t>0.7681,0.3764,0.0034,0.0006</t>
-  </si>
-  <si>
-    <t>0.9852,0.0041,0.0053,0.0002</t>
-  </si>
-  <si>
-    <t>0.8995,0.0239,0.0827,0.0008</t>
-  </si>
-  <si>
-    <t>0.9807,0.0044,0.0092,0.0009</t>
-  </si>
-  <si>
-    <t>0.9568,0.0214,0.0173,0.0005</t>
-  </si>
-  <si>
-    <t>0.9325,0.0225,0.0199,0.0041</t>
-  </si>
-  <si>
-    <t>0.8324,0.1932,0.0092,0.0001</t>
-  </si>
-  <si>
-    <t>0.8360,0.2504,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.8935,0.1129,0.0100,0.0003</t>
-  </si>
-  <si>
-    <t>0.8585,0.1816,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.9513,0.0890,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9653,0.0338,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.7952,0.2854,0.0056,0.0007</t>
-  </si>
-  <si>
-    <t>0.9927,0.0040,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.8973,0.1392,0.0042,0.0008</t>
-  </si>
-  <si>
-    <t>0.8176,0.2112,0.0100,0.0016</t>
-  </si>
-  <si>
-    <t>0.8892,0.1268,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.9741,0.0196,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9485,0.0514,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.9279,0.0832,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.9290,0.0825,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9682,0.0014,0.0692,0.0003</t>
-  </si>
-  <si>
-    <t>0.8257,0.0126,0.1648,0.0003</t>
-  </si>
-  <si>
-    <t>0.7910,0.0088,0.3129,0.0009</t>
-  </si>
-  <si>
-    <t>0.9255,0.0073,0.1098,0.0012</t>
-  </si>
-  <si>
-    <t>0.9655,0.0285,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9880,0.0047,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9434,0.0084,0.0569,0.0012</t>
-  </si>
-  <si>
-    <t>0.9308,0.0414,0.0098,0.0005</t>
-  </si>
-  <si>
-    <t>0.9715,0.0106,0.0044,0.0014</t>
-  </si>
-  <si>
-    <t>0.7621,0.0228,0.0476,0.1317</t>
-  </si>
-  <si>
-    <t>0.9229,0.0169,0.0308,0.0103</t>
-  </si>
-  <si>
-    <t>0.8706,0.0536,0.0173,0.0121</t>
-  </si>
-  <si>
-    <t>0.3132,0.0221,0.7178,0.0008</t>
-  </si>
-  <si>
-    <t>0.9683,0.0239,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.9672,0.0340,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.7151,0.3793,0.0089,0.0008</t>
-  </si>
-  <si>
-    <t>0.9420,0.0702,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9123,0.0774,0.0067,0.0018</t>
-  </si>
-  <si>
-    <t>0.8757,0.1267,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.9093,0.0995,0.0059,0.0008</t>
-  </si>
-  <si>
-    <t>0.6324,0.0967,0.4581,0.0197</t>
-  </si>
-  <si>
-    <t>0.9342,0.0498,0.0070,0.0008</t>
-  </si>
-  <si>
-    <t>0.6791,0.3911,0.0084,0.0024</t>
-  </si>
-  <si>
-    <t>0.9085,0.0993,0.0056,0.0005</t>
-  </si>
-  <si>
-    <t>0.9757,0.0172,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.7371,0.3124,0.0104,0.0010</t>
-  </si>
-  <si>
-    <t>0.8559,0.2042,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9795,0.0163,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9587,0.0465,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.6955,0.4118,0.0076,0.0010</t>
-  </si>
-  <si>
-    <t>0.9141,0.0794,0.0028,0.0013</t>
-  </si>
-  <si>
-    <t>0.8735,0.1581,0.0026,0.0009</t>
-  </si>
-  <si>
-    <t>0.7894,0.2408,0.0084,0.0023</t>
-  </si>
-  <si>
-    <t>0.9714,0.0271,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.7419,0.3818,0.0063,0.0008</t>
-  </si>
-  <si>
-    <t>0.9444,0.0715,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9523,0.0428,0.0028,0.0010</t>
-  </si>
-  <si>
-    <t>0.8759,0.1740,0.0052,0.0005</t>
-  </si>
-  <si>
-    <t>0.9221,0.0942,0.0042,0.0004</t>
-  </si>
-  <si>
-    <t>0.4090,0.7590,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.7851,0.1904,0.0250,0.0003</t>
-  </si>
-  <si>
-    <t>0.9037,0.1278,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9446,0.0574,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.8907,0.1611,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.8791,0.1712,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.2569,0.3408,0.2069,0.0002</t>
-  </si>
-  <si>
-    <t>0.9739,0.0170,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.7164,0.0043,0.4327,0.0010</t>
-  </si>
-  <si>
-    <t>0.9748,0.0027,0.0342,0.0003</t>
-  </si>
-  <si>
-    <t>0.1713,0.3641,0.3786,0.0010</t>
-  </si>
-  <si>
-    <t>0.7651,0.0267,0.1780,0.0001</t>
-  </si>
-  <si>
-    <t>0.7254,0.0258,0.2343,0.0024</t>
-  </si>
-  <si>
-    <t>0.6298,0.0123,0.5138,0.0029</t>
-  </si>
-  <si>
-    <t>0.8869,0.0116,0.1414,0.0010</t>
-  </si>
-  <si>
-    <t>0.8296,0.0138,0.2295,0.0021</t>
-  </si>
-  <si>
-    <t>0.7828,0.0484,0.2008,0.0017</t>
-  </si>
-  <si>
-    <t>0.9209,0.0170,0.0657,0.0008</t>
-  </si>
-  <si>
-    <t>0.8431,0.1286,0.0204,0.0002</t>
-  </si>
-  <si>
-    <t>0.8971,0.0664,0.0201,0.0005</t>
-  </si>
-  <si>
-    <t>0.9759,0.0069,0.0089,0.0002</t>
-  </si>
-  <si>
-    <t>0.7477,0.2128,0.0532,0.0025</t>
-  </si>
-  <si>
-    <t>0.9389,0.0375,0.0101,0.0009</t>
-  </si>
-  <si>
-    <t>0.9473,0.0622,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.7229,0.4002,0.0046,0.0007</t>
-  </si>
-  <si>
-    <t>0.7049,0.4317,0.0039,0.0006</t>
-  </si>
-  <si>
-    <t>0.9317,0.0750,0.0024,0.0009</t>
-  </si>
-  <si>
-    <t>0.7337,0.4313,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.9832,0.0019,0.0137,0.0001</t>
-  </si>
-  <si>
-    <t>0.9700,0.0126,0.0072,0.0008</t>
-  </si>
-  <si>
-    <t>0.9876,0.0027,0.0056,0.0001</t>
-  </si>
-  <si>
-    <t>0.9771,0.0041,0.0184,0.0003</t>
-  </si>
-  <si>
-    <t>0.9788,0.0050,0.0088,0.0005</t>
-  </si>
-  <si>
-    <t>0.6153,0.1182,0.1380,0.0005</t>
-  </si>
-  <si>
-    <t>0.9901,0.0008,0.0114,0.0001</t>
-  </si>
-  <si>
-    <t>0.9204,0.0014,0.1798,0.0009</t>
-  </si>
-  <si>
-    <t>0.9837,0.0007,0.0356,0.0001</t>
-  </si>
-  <si>
-    <t>0.9446,0.0055,0.0563,0.0005</t>
-  </si>
-  <si>
-    <t>0.8981,0.0818,0.0043,0.0020</t>
-  </si>
-  <si>
-    <t>0.8966,0.1409,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.8811,0.1570,0.0031,0.0005</t>
-  </si>
-  <si>
-    <t>0.8704,0.1253,0.0039,0.0015</t>
-  </si>
-  <si>
-    <t>0.9056,0.0773,0.0062,0.0027</t>
-  </si>
-  <si>
-    <t>0.9184,0.1099,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9187,0.1236,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.6812,0.4183,0.0108,0.0017</t>
-  </si>
-  <si>
-    <t>0.8471,0.0982,0.0567,0.0017</t>
-  </si>
-  <si>
-    <t>0.8960,0.0884,0.0102,0.0011</t>
-  </si>
-  <si>
-    <t>0.8745,0.1012,0.0168,0.0031</t>
-  </si>
-  <si>
-    <t>0.4722,0.0128,0.7197,0.0009</t>
-  </si>
-  <si>
-    <t>0.0257,0.0076,0.9780,0.0009</t>
-  </si>
-  <si>
-    <t>0.7730,0.0142,0.3351,0.0016</t>
-  </si>
-  <si>
-    <t>0.0566,0.0076,0.9592,0.0004</t>
-  </si>
-  <si>
-    <t>0.5947,0.0202,0.4698,0.0005</t>
-  </si>
-  <si>
-    <t>0.0039,0.0045,0.9918,0.0020</t>
-  </si>
-  <si>
-    <t>0.9545,0.0007,0.1105,0.0004</t>
-  </si>
-  <si>
-    <t>0.9710,0.0097,0.0154,0.0003</t>
-  </si>
-  <si>
-    <t>0.9708,0.0110,0.0069,0.0009</t>
-  </si>
-  <si>
-    <t>0.9888,0.0021,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.9836,0.0026,0.0089,0.0004</t>
-  </si>
-  <si>
-    <t>0.9468,0.0572,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.8526,0.1254,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.9543,0.0351,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.7647,0.3219,0.0080,0.0016</t>
-  </si>
-  <si>
-    <t>0.8559,0.1747,0.0062,0.0016</t>
-  </si>
-  <si>
-    <t>0.9141,0.0805,0.0037,0.0015</t>
-  </si>
-  <si>
-    <t>0.9397,0.0379,0.0022,0.0016</t>
-  </si>
-  <si>
-    <t>0.6738,0.4493,0.0046,0.0006</t>
-  </si>
-  <si>
-    <t>0.9685,0.0048,0.0355,0.0006</t>
-  </si>
-  <si>
-    <t>0.1458,0.0065,0.9243,0.0006</t>
-  </si>
-  <si>
-    <t>0.1736,0.2546,0.5550,0.0013</t>
-  </si>
-  <si>
-    <t>0.8927,0.0136,0.0990,0.0007</t>
-  </si>
-  <si>
-    <t>0.8780,0.0029,0.2350,0.0004</t>
-  </si>
-  <si>
-    <t>0.8864,0.0058,0.1471,0.0037</t>
-  </si>
-  <si>
-    <t>0.8756,0.0123,0.1794,0.0040</t>
-  </si>
-  <si>
-    <t>0.9815,0.0007,0.0320,0.0002</t>
-  </si>
-  <si>
-    <t>0.9770,0.0087,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.9646,0.0063,0.0123,0.0037</t>
-  </si>
-  <si>
-    <t>0.9514,0.0153,0.0135,0.0040</t>
-  </si>
-  <si>
-    <t>0.9325,0.0161,0.0164,0.0123</t>
-  </si>
-  <si>
-    <t>0.8593,0.0532,0.0414,0.0231</t>
-  </si>
-  <si>
-    <t>0.9510,0.0198,0.0196,0.0012</t>
+    <t>0.9468,0.0331,0.0076,0.0008</t>
+  </si>
+  <si>
+    <t>0.9658,0.0083,0.0037,0.0035</t>
+  </si>
+  <si>
+    <t>0.9185,0.0581,0.0104,0.0028</t>
+  </si>
+  <si>
+    <t>0.7636,0.1045,0.0287,0.0244</t>
+  </si>
+  <si>
+    <t>0.9623,0.0271,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.7505,0.2982,0.0053,0.0011</t>
+  </si>
+  <si>
+    <t>0.7938,0.2987,0.0077,0.0008</t>
+  </si>
+  <si>
+    <t>0.8076,0.2323,0.0076,0.0011</t>
+  </si>
+  <si>
+    <t>0.8242,0.2329,0.0068,0.0015</t>
+  </si>
+  <si>
+    <t>0.9775,0.0141,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9272,0.0823,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.9108,0.1221,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9605,0.0184,0.0121,0.0004</t>
+  </si>
+  <si>
+    <t>0.9342,0.0315,0.0200,0.0007</t>
+  </si>
+  <si>
+    <t>0.9677,0.0110,0.0169,0.0002</t>
+  </si>
+  <si>
+    <t>0.9763,0.0034,0.0225,0.0003</t>
+  </si>
+  <si>
+    <t>0.9589,0.0303,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.7219,0.4392,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.2546,0.8597,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.9047,0.0890,0.0137,0.0019</t>
+  </si>
+  <si>
+    <t>0.8708,0.1947,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.0802,0.9592,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.9745,0.0039,0.0223,0.0006</t>
+  </si>
+  <si>
+    <t>0.9860,0.0007,0.0217,0.0001</t>
+  </si>
+  <si>
+    <t>0.9273,0.0026,0.1231,0.0011</t>
+  </si>
+  <si>
+    <t>0.9557,0.0042,0.0502,0.0004</t>
+  </si>
+  <si>
+    <t>0.9409,0.0166,0.0467,0.0005</t>
+  </si>
+  <si>
+    <t>0.9557,0.0081,0.0343,0.0009</t>
+  </si>
+  <si>
+    <t>0.1362,0.0334,0.8353,0.0017</t>
+  </si>
+  <si>
+    <t>0.9792,0.0219,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9292,0.0633,0.0054,0.0006</t>
+  </si>
+  <si>
+    <t>0.0064,0.1522,0.9834,0.0011</t>
+  </si>
+  <si>
+    <t>0.3104,0.6189,0.0449,0.0005</t>
+  </si>
+  <si>
+    <t>0.9051,0.0877,0.0065,0.0010</t>
+  </si>
+  <si>
+    <t>0.9833,0.0112,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.6887,0.4242,0.0115,0.0013</t>
+  </si>
+  <si>
+    <t>0.9777,0.0230,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.5427,0.0174,0.5059,0.0022</t>
+  </si>
+  <si>
+    <t>0.9575,0.0008,0.0976,0.0010</t>
+  </si>
+  <si>
+    <t>0.9469,0.0033,0.0864,0.0005</t>
+  </si>
+  <si>
+    <t>0.8773,0.0018,0.2739,0.0004</t>
+  </si>
+  <si>
+    <t>0.9195,0.0007,0.1980,0.0001</t>
+  </si>
+  <si>
+    <t>0.2746,0.0251,0.5922,0.0004</t>
+  </si>
+  <si>
+    <t>0.9568,0.0013,0.0977,0.0003</t>
+  </si>
+  <si>
+    <t>0.8218,0.2144,0.0130,0.0008</t>
+  </si>
+  <si>
+    <t>0.3457,0.8045,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.9858,0.0090,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.9186,0.1027,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.0311,0.0284,0.9669,0.0008</t>
+  </si>
+  <si>
+    <t>0.1739,0.0976,0.7983,0.0044</t>
+  </si>
+  <si>
+    <t>0.9911,0.0005,0.0156,0.0001</t>
+  </si>
+  <si>
+    <t>0.9528,0.0045,0.0562,0.0008</t>
+  </si>
+  <si>
+    <t>0.0103,0.0022,0.9924,0.0002</t>
+  </si>
+  <si>
+    <t>0.9580,0.0035,0.0468,0.0001</t>
+  </si>
+  <si>
+    <t>0.9446,0.0495,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.8776,0.1263,0.0067,0.0020</t>
+  </si>
+  <si>
+    <t>0.8790,0.1238,0.0046,0.0009</t>
+  </si>
+  <si>
+    <t>0.0369,0.5132,0.9034,0.0062</t>
+  </si>
+  <si>
+    <t>0.8805,0.1183,0.0030,0.0019</t>
+  </si>
+  <si>
+    <t>0.9313,0.0400,0.0026,0.0035</t>
+  </si>
+  <si>
+    <t>0.8661,0.1665,0.0068,0.0010</t>
+  </si>
+  <si>
+    <t>0.1697,0.6307,0.3197,0.0004</t>
+  </si>
+  <si>
+    <t>0.3600,0.0051,0.8527,0.0002</t>
+  </si>
+  <si>
+    <t>0.8382,0.0081,0.2689,0.0021</t>
+  </si>
+  <si>
+    <t>0.5398,0.0776,0.4066,0.0014</t>
+  </si>
+  <si>
+    <t>0.1320,0.0080,0.9135,0.0007</t>
+  </si>
+  <si>
+    <t>0.8945,0.1525,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.3565,0.7810,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.9420,0.0486,0.0084,0.0007</t>
+  </si>
+  <si>
+    <t>0.9312,0.0901,0.0040,0.0003</t>
+  </si>
+  <si>
+    <t>0.0843,0.1940,0.8786,0.0185</t>
+  </si>
+  <si>
+    <t>0.7252,0.1169,0.0549,0.0005</t>
+  </si>
+  <si>
+    <t>0.8955,0.0079,0.1455,0.0004</t>
+  </si>
+  <si>
+    <t>0.5489,0.4014,0.0356,0.0004</t>
+  </si>
+  <si>
+    <t>0.2990,0.3564,0.2074,0.0003</t>
+  </si>
+  <si>
+    <t>0.9158,0.0153,0.0652,0.0105</t>
+  </si>
+  <si>
+    <t>0.9511,0.0147,0.0054,0.0060</t>
+  </si>
+  <si>
+    <t>0.8822,0.0499,0.0598,0.0067</t>
+  </si>
+  <si>
+    <t>0.9731,0.0066,0.0062,0.0028</t>
+  </si>
+  <si>
+    <t>0.9397,0.0285,0.0058,0.0049</t>
+  </si>
+  <si>
+    <t>0.9539,0.0140,0.0068,0.0038</t>
+  </si>
+  <si>
+    <t>0.3747,0.5073,0.0929,0.0001</t>
+  </si>
+  <si>
+    <t>0.8088,0.0068,0.2943,0.0007</t>
+  </si>
+  <si>
+    <t>0.3545,0.0547,0.5908,0.0034</t>
+  </si>
+  <si>
+    <t>0.9166,0.0034,0.1692,0.0010</t>
+  </si>
+  <si>
+    <t>0.5248,0.4636,0.0078,0.0000</t>
+  </si>
+  <si>
+    <t>0.8356,0.0569,0.0576,0.0007</t>
+  </si>
+  <si>
+    <t>0.8350,0.2225,0.0032,0.0007</t>
+  </si>
+  <si>
+    <t>0.9602,0.0259,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.9164,0.0882,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.8206,0.2262,0.0048,0.0013</t>
+  </si>
+  <si>
+    <t>0.9754,0.0171,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9373,0.0527,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.8225,0.2318,0.0048,0.0013</t>
+  </si>
+  <si>
+    <t>0.8288,0.2221,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9290,0.0682,0.0026,0.0013</t>
+  </si>
+  <si>
+    <t>0.8130,0.1783,0.0118,0.0041</t>
+  </si>
+  <si>
+    <t>0.8790,0.0969,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9266,0.0839,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.8602,0.1704,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.9516,0.0305,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.8131,0.2091,0.0045,0.0014</t>
+  </si>
+  <si>
+    <t>0.8199,0.1935,0.0051,0.0023</t>
+  </si>
+  <si>
+    <t>0.1052,0.0289,0.9405,0.0006</t>
+  </si>
+  <si>
+    <t>0.6488,0.0543,0.2647,0.0016</t>
+  </si>
+  <si>
+    <t>0.9930,0.0006,0.0059,0.0002</t>
+  </si>
+  <si>
+    <t>0.9334,0.0195,0.0405,0.0011</t>
+  </si>
+  <si>
+    <t>0.0622,0.9615,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.7792,0.3319,0.0048,0.0004</t>
+  </si>
+  <si>
+    <t>0.7419,0.3354,0.0157,0.0021</t>
+  </si>
+  <si>
+    <t>0.5774,0.5348,0.0143,0.0008</t>
+  </si>
+  <si>
+    <t>0.7719,0.3896,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.2850,0.8396,0.0048,0.0005</t>
+  </si>
+  <si>
+    <t>0.9328,0.0874,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.8531,0.1058,0.0256,0.0013</t>
+  </si>
+  <si>
+    <t>0.7626,0.0025,0.4530,0.0006</t>
+  </si>
+  <si>
+    <t>0.8922,0.0638,0.0271,0.0008</t>
+  </si>
+  <si>
+    <t>0.9272,0.0620,0.0066,0.0001</t>
+  </si>
+  <si>
+    <t>0.8605,0.0790,0.0518,0.0059</t>
+  </si>
+  <si>
+    <t>0.9517,0.0825,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.8203,0.1839,0.0087,0.0001</t>
+  </si>
+  <si>
+    <t>0.9221,0.0723,0.0053,0.0001</t>
+  </si>
+  <si>
+    <t>0.0295,0.1662,0.8866,0.0004</t>
+  </si>
+  <si>
+    <t>0.9700,0.0306,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.6062,0.4641,0.0078,0.0012</t>
+  </si>
+  <si>
+    <t>0.7981,0.2519,0.0087,0.0010</t>
+  </si>
+  <si>
+    <t>0.9804,0.0141,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9672,0.0318,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9438,0.0444,0.0035,0.0014</t>
+  </si>
+  <si>
+    <t>0.8596,0.0984,0.0065,0.0044</t>
+  </si>
+  <si>
+    <t>0.8548,0.1969,0.0061,0.0011</t>
+  </si>
+  <si>
+    <t>0.9527,0.0535,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.6800,0.3237,0.0252,0.0022</t>
+  </si>
+  <si>
+    <t>0.7948,0.2101,0.0173,0.0039</t>
+  </si>
+  <si>
+    <t>0.9573,0.0013,0.0985,0.0001</t>
+  </si>
+  <si>
+    <t>0.6590,0.1431,0.1096,0.0007</t>
+  </si>
+  <si>
+    <t>0.7249,0.0044,0.4713,0.0012</t>
+  </si>
+  <si>
+    <t>0.9681,0.0035,0.0379,0.0002</t>
+  </si>
+  <si>
+    <t>0.9474,0.0262,0.0121,0.0011</t>
+  </si>
+  <si>
+    <t>0.9595,0.0369,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.9305,0.0291,0.0280,0.0012</t>
+  </si>
+  <si>
+    <t>0.9246,0.0571,0.0093,0.0008</t>
+  </si>
+  <si>
+    <t>0.9652,0.0070,0.0028,0.0048</t>
+  </si>
+  <si>
+    <t>0.8397,0.0494,0.0550,0.0340</t>
+  </si>
+  <si>
+    <t>0.9531,0.0179,0.0095,0.0034</t>
+  </si>
+  <si>
+    <t>0.9628,0.0064,0.0034,0.0104</t>
+  </si>
+  <si>
+    <t>0.1721,0.7157,0.0630,0.0003</t>
+  </si>
+  <si>
+    <t>0.9248,0.0647,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.9066,0.0827,0.0168,0.0018</t>
+  </si>
+  <si>
+    <t>0.8453,0.1976,0.0094,0.0018</t>
+  </si>
+  <si>
+    <t>0.9624,0.0378,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.8159,0.2256,0.0066,0.0019</t>
+  </si>
+  <si>
+    <t>0.9033,0.0685,0.0058,0.0012</t>
+  </si>
+  <si>
+    <t>0.5669,0.4475,0.0058,0.0020</t>
+  </si>
+  <si>
+    <t>0.4270,0.1475,0.6299,0.0226</t>
+  </si>
+  <si>
+    <t>0.9458,0.0341,0.0082,0.0012</t>
+  </si>
+  <si>
+    <t>0.9604,0.0208,0.0025,0.0015</t>
+  </si>
+  <si>
+    <t>0.9507,0.0259,0.0092,0.0013</t>
+  </si>
+  <si>
+    <t>0.9200,0.0677,0.0074,0.0006</t>
+  </si>
+  <si>
+    <t>0.9045,0.1249,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.9513,0.0401,0.0054,0.0006</t>
+  </si>
+  <si>
+    <t>0.9098,0.1176,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.8987,0.1388,0.0064,0.0002</t>
+  </si>
+  <si>
+    <t>0.9578,0.0324,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.9231,0.0648,0.0026,0.0022</t>
+  </si>
+  <si>
+    <t>0.9328,0.0836,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9147,0.0752,0.0045,0.0019</t>
+  </si>
+  <si>
+    <t>0.9694,0.0185,0.0018,0.0012</t>
+  </si>
+  <si>
+    <t>0.8792,0.1367,0.0053,0.0013</t>
+  </si>
+  <si>
+    <t>0.9639,0.0294,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.8203,0.1924,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.8979,0.1079,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.6449,0.5459,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.9798,0.0161,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.4850,0.4456,0.1264,0.0017</t>
+  </si>
+  <si>
+    <t>0.9107,0.0878,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.7008,0.4239,0.0121,0.0011</t>
+  </si>
+  <si>
+    <t>0.9701,0.0408,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.5111,0.6316,0.0058,0.0006</t>
+  </si>
+  <si>
+    <t>0.0254,0.5715,0.8242,0.0004</t>
+  </si>
+  <si>
+    <t>0.9063,0.1047,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.4410,0.0064,0.7076,0.0026</t>
+  </si>
+  <si>
+    <t>0.9846,0.0011,0.0260,0.0001</t>
+  </si>
+  <si>
+    <t>0.6611,0.0483,0.3254,0.0041</t>
+  </si>
+  <si>
+    <t>0.5284,0.0090,0.5918,0.0005</t>
+  </si>
+  <si>
+    <t>0.9703,0.0014,0.0560,0.0003</t>
+  </si>
+  <si>
+    <t>0.4833,0.0066,0.6764,0.0008</t>
+  </si>
+  <si>
+    <t>0.4904,0.0063,0.7296,0.0007</t>
+  </si>
+  <si>
+    <t>0.9533,0.0341,0.0081,0.0002</t>
+  </si>
+  <si>
+    <t>0.9698,0.0165,0.0084,0.0003</t>
+  </si>
+  <si>
+    <t>0.9437,0.0240,0.0242,0.0008</t>
+  </si>
+  <si>
+    <t>0.7928,0.2603,0.0070,0.0002</t>
+  </si>
+  <si>
+    <t>0.9526,0.0361,0.0062,0.0001</t>
+  </si>
+  <si>
+    <t>0.9133,0.0520,0.0152,0.0002</t>
+  </si>
+  <si>
+    <t>0.8614,0.0616,0.0632,0.0018</t>
+  </si>
+  <si>
+    <t>0.9675,0.0110,0.0102,0.0006</t>
+  </si>
+  <si>
+    <t>0.3788,0.7920,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.7328,0.3731,0.0063,0.0014</t>
+  </si>
+  <si>
+    <t>0.5579,0.5881,0.0070,0.0009</t>
+  </si>
+  <si>
+    <t>0.9713,0.0328,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.5183,0.6724,0.0055,0.0004</t>
+  </si>
+  <si>
+    <t>0.9144,0.0404,0.0223,0.0015</t>
+  </si>
+  <si>
+    <t>0.9276,0.0519,0.0134,0.0005</t>
+  </si>
+  <si>
+    <t>0.9610,0.0086,0.0231,0.0023</t>
+  </si>
+  <si>
+    <t>0.9495,0.0130,0.0463,0.0007</t>
+  </si>
+  <si>
+    <t>0.8725,0.0288,0.1189,0.0054</t>
+  </si>
+  <si>
+    <t>0.3588,0.0140,0.6932,0.0052</t>
+  </si>
+  <si>
+    <t>0.7448,0.0040,0.3595,0.0002</t>
+  </si>
+  <si>
+    <t>0.9943,0.0005,0.0054,0.0001</t>
+  </si>
+  <si>
+    <t>0.9465,0.0012,0.0895,0.0010</t>
+  </si>
+  <si>
+    <t>0.9175,0.0335,0.0229,0.0003</t>
+  </si>
+  <si>
+    <t>0.8237,0.1606,0.0063,0.0025</t>
+  </si>
+  <si>
+    <t>0.9268,0.0733,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.8514,0.1999,0.0051,0.0011</t>
+  </si>
+  <si>
+    <t>0.9657,0.0322,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.7205,0.2214,0.0060,0.0045</t>
+  </si>
+  <si>
+    <t>0.8902,0.1261,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.7130,0.3846,0.0084,0.0025</t>
+  </si>
+  <si>
+    <t>0.7375,0.3490,0.0043,0.0008</t>
+  </si>
+  <si>
+    <t>0.9132,0.0460,0.0447,0.0017</t>
+  </si>
+  <si>
+    <t>0.8659,0.1072,0.0339,0.0009</t>
+  </si>
+  <si>
+    <t>0.5346,0.5021,0.0546,0.0038</t>
+  </si>
+  <si>
+    <t>0.9254,0.0027,0.1180,0.0002</t>
+  </si>
+  <si>
+    <t>0.0658,0.0091,0.9539,0.0009</t>
+  </si>
+  <si>
+    <t>0.9178,0.0180,0.0743,0.0011</t>
+  </si>
+  <si>
+    <t>0.0104,0.0044,0.9929,0.0001</t>
+  </si>
+  <si>
+    <t>0.8343,0.0160,0.1904,0.0007</t>
+  </si>
+  <si>
+    <t>0.0525,0.0343,0.9380,0.0048</t>
+  </si>
+  <si>
+    <t>0.9491,0.0018,0.1123,0.0002</t>
+  </si>
+  <si>
+    <t>0.3300,0.4437,0.2920,0.0054</t>
+  </si>
+  <si>
+    <t>0.9444,0.0416,0.0091,0.0004</t>
+  </si>
+  <si>
+    <t>0.9579,0.0068,0.0472,0.0007</t>
+  </si>
+  <si>
+    <t>0.9852,0.0027,0.0080,0.0006</t>
+  </si>
+  <si>
+    <t>0.8323,0.2176,0.0047,0.0013</t>
+  </si>
+  <si>
+    <t>0.9564,0.0310,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.7569,0.2855,0.0126,0.0028</t>
+  </si>
+  <si>
+    <t>0.8816,0.1109,0.0023,0.0013</t>
+  </si>
+  <si>
+    <t>0.9507,0.0327,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9173,0.1172,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.8173,0.2301,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.7394,0.3242,0.0050,0.0012</t>
+  </si>
+  <si>
+    <t>0.9149,0.0063,0.1287,0.0004</t>
+  </si>
+  <si>
+    <t>0.8246,0.0046,0.3193,0.0003</t>
+  </si>
+  <si>
+    <t>0.7089,0.0178,0.3591,0.0036</t>
+  </si>
+  <si>
+    <t>0.6210,0.0219,0.3878,0.0011</t>
+  </si>
+  <si>
+    <t>0.7428,0.0017,0.4641,0.0001</t>
+  </si>
+  <si>
+    <t>0.9679,0.0043,0.0254,0.0010</t>
+  </si>
+  <si>
+    <t>0.9795,0.0037,0.0171,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0001,0.0047,0.0000</t>
+  </si>
+  <si>
+    <t>0.9582,0.0367,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9124,0.0143,0.0581,0.0098</t>
+  </si>
+  <si>
+    <t>0.9596,0.0134,0.0055,0.0027</t>
+  </si>
+  <si>
+    <t>0.9774,0.0028,0.0032,0.0049</t>
+  </si>
+  <si>
+    <t>0.9669,0.0047,0.0030,0.0154</t>
+  </si>
+  <si>
+    <t>0.9354,0.0512,0.0059,0.0004</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D223" t="s">
         <v>485</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9468,0.0331,0.0076,0.0008</t>
-  </si>
-  <si>
-    <t>0.9658,0.0083,0.0037,0.0035</t>
-  </si>
-  <si>
-    <t>0.9185,0.0581,0.0104,0.0028</t>
-  </si>
-  <si>
-    <t>0.7636,0.1045,0.0287,0.0244</t>
-  </si>
-  <si>
-    <t>0.9623,0.0271,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.7505,0.2982,0.0053,0.0011</t>
-  </si>
-  <si>
-    <t>0.7938,0.2987,0.0077,0.0008</t>
-  </si>
-  <si>
-    <t>0.8076,0.2323,0.0076,0.0011</t>
-  </si>
-  <si>
-    <t>0.8242,0.2329,0.0068,0.0015</t>
-  </si>
-  <si>
-    <t>0.9775,0.0141,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9272,0.0823,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9108,0.1221,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9605,0.0184,0.0121,0.0004</t>
-  </si>
-  <si>
-    <t>0.9342,0.0315,0.0200,0.0007</t>
-  </si>
-  <si>
-    <t>0.9677,0.0110,0.0169,0.0002</t>
-  </si>
-  <si>
-    <t>0.9763,0.0034,0.0225,0.0003</t>
-  </si>
-  <si>
-    <t>0.9589,0.0303,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.7219,0.4392,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.2546,0.8597,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.9047,0.0890,0.0137,0.0019</t>
-  </si>
-  <si>
-    <t>0.8708,0.1947,0.0061,0.0002</t>
-  </si>
-  <si>
-    <t>0.0802,0.9592,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.9745,0.0039,0.0223,0.0006</t>
-  </si>
-  <si>
-    <t>0.9860,0.0007,0.0217,0.0001</t>
-  </si>
-  <si>
-    <t>0.9273,0.0026,0.1231,0.0011</t>
-  </si>
-  <si>
-    <t>0.9557,0.0042,0.0502,0.0004</t>
-  </si>
-  <si>
-    <t>0.9409,0.0166,0.0467,0.0005</t>
-  </si>
-  <si>
-    <t>0.9557,0.0081,0.0343,0.0009</t>
-  </si>
-  <si>
-    <t>0.1362,0.0334,0.8353,0.0017</t>
-  </si>
-  <si>
-    <t>0.9792,0.0219,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9292,0.0633,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.0064,0.1522,0.9834,0.0011</t>
-  </si>
-  <si>
-    <t>0.3104,0.6189,0.0449,0.0005</t>
-  </si>
-  <si>
-    <t>0.9051,0.0877,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.9833,0.0112,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.6887,0.4242,0.0115,0.0013</t>
-  </si>
-  <si>
-    <t>0.9777,0.0230,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.5427,0.0174,0.5059,0.0022</t>
-  </si>
-  <si>
-    <t>0.9575,0.0008,0.0976,0.0010</t>
-  </si>
-  <si>
-    <t>0.9469,0.0033,0.0864,0.0005</t>
-  </si>
-  <si>
-    <t>0.8773,0.0018,0.2739,0.0004</t>
-  </si>
-  <si>
-    <t>0.9195,0.0007,0.1980,0.0001</t>
-  </si>
-  <si>
-    <t>0.2746,0.0251,0.5922,0.0004</t>
-  </si>
-  <si>
-    <t>0.9568,0.0013,0.0977,0.0003</t>
-  </si>
-  <si>
-    <t>0.8218,0.2144,0.0130,0.0008</t>
-  </si>
-  <si>
-    <t>0.3457,0.8045,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9858,0.0090,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.9186,0.1027,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.0311,0.0284,0.9669,0.0008</t>
-  </si>
-  <si>
-    <t>0.1739,0.0976,0.7983,0.0044</t>
-  </si>
-  <si>
-    <t>0.9911,0.0005,0.0156,0.0001</t>
-  </si>
-  <si>
-    <t>0.9528,0.0045,0.0562,0.0008</t>
-  </si>
-  <si>
-    <t>0.0103,0.0022,0.9924,0.0002</t>
-  </si>
-  <si>
-    <t>0.9580,0.0035,0.0468,0.0001</t>
-  </si>
-  <si>
-    <t>0.9446,0.0495,0.0014,0.0009</t>
-  </si>
-  <si>
-    <t>0.8776,0.1263,0.0067,0.0020</t>
-  </si>
-  <si>
-    <t>0.8790,0.1238,0.0046,0.0009</t>
-  </si>
-  <si>
-    <t>0.0369,0.5132,0.9034,0.0062</t>
-  </si>
-  <si>
-    <t>0.8805,0.1183,0.0030,0.0019</t>
-  </si>
-  <si>
-    <t>0.9313,0.0400,0.0026,0.0035</t>
-  </si>
-  <si>
-    <t>0.8661,0.1665,0.0068,0.0010</t>
-  </si>
-  <si>
-    <t>0.1697,0.6307,0.3197,0.0004</t>
-  </si>
-  <si>
-    <t>0.3600,0.0051,0.8527,0.0002</t>
-  </si>
-  <si>
-    <t>0.8382,0.0081,0.2689,0.0021</t>
-  </si>
-  <si>
-    <t>0.5398,0.0776,0.4066,0.0014</t>
-  </si>
-  <si>
-    <t>0.1320,0.0080,0.9135,0.0007</t>
-  </si>
-  <si>
-    <t>0.8945,0.1525,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.3565,0.7810,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9420,0.0486,0.0084,0.0007</t>
-  </si>
-  <si>
-    <t>0.9312,0.0901,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.0843,0.1940,0.8786,0.0185</t>
-  </si>
-  <si>
-    <t>0.7252,0.1169,0.0549,0.0005</t>
-  </si>
-  <si>
-    <t>0.8955,0.0079,0.1455,0.0004</t>
-  </si>
-  <si>
-    <t>0.5489,0.4014,0.0356,0.0004</t>
-  </si>
-  <si>
-    <t>0.2990,0.3564,0.2074,0.0003</t>
-  </si>
-  <si>
-    <t>0.9158,0.0153,0.0652,0.0105</t>
-  </si>
-  <si>
-    <t>0.9511,0.0147,0.0054,0.0060</t>
-  </si>
-  <si>
-    <t>0.8822,0.0499,0.0598,0.0067</t>
-  </si>
-  <si>
-    <t>0.9731,0.0066,0.0062,0.0028</t>
-  </si>
-  <si>
-    <t>0.9397,0.0285,0.0058,0.0049</t>
-  </si>
-  <si>
-    <t>0.9539,0.0140,0.0068,0.0038</t>
-  </si>
-  <si>
-    <t>0.3747,0.5073,0.0929,0.0001</t>
-  </si>
-  <si>
-    <t>0.8088,0.0068,0.2943,0.0007</t>
-  </si>
-  <si>
-    <t>0.3545,0.0547,0.5908,0.0034</t>
-  </si>
-  <si>
-    <t>0.9166,0.0034,0.1692,0.0010</t>
-  </si>
-  <si>
-    <t>0.5248,0.4636,0.0078,0.0000</t>
-  </si>
-  <si>
-    <t>0.8356,0.0569,0.0576,0.0007</t>
-  </si>
-  <si>
-    <t>0.8350,0.2225,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.9602,0.0259,0.0014,0.0012</t>
-  </si>
-  <si>
-    <t>0.9164,0.0882,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.8206,0.2262,0.0048,0.0013</t>
-  </si>
-  <si>
-    <t>0.9754,0.0171,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9373,0.0527,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.8225,0.2318,0.0048,0.0013</t>
-  </si>
-  <si>
-    <t>0.8288,0.2221,0.0020,0.0011</t>
-  </si>
-  <si>
-    <t>0.9290,0.0682,0.0026,0.0013</t>
-  </si>
-  <si>
-    <t>0.8130,0.1783,0.0118,0.0041</t>
-  </si>
-  <si>
-    <t>0.8790,0.0969,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9266,0.0839,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.8602,0.1704,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.9516,0.0305,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.8131,0.2091,0.0045,0.0014</t>
-  </si>
-  <si>
-    <t>0.8199,0.1935,0.0051,0.0023</t>
-  </si>
-  <si>
-    <t>0.1052,0.0289,0.9405,0.0006</t>
-  </si>
-  <si>
-    <t>0.6488,0.0543,0.2647,0.0016</t>
-  </si>
-  <si>
-    <t>0.9930,0.0006,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.9334,0.0195,0.0405,0.0011</t>
-  </si>
-  <si>
-    <t>0.0622,0.9615,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.7792,0.3319,0.0048,0.0004</t>
-  </si>
-  <si>
-    <t>0.7419,0.3354,0.0157,0.0021</t>
-  </si>
-  <si>
-    <t>0.5774,0.5348,0.0143,0.0008</t>
-  </si>
-  <si>
-    <t>0.7719,0.3896,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.2850,0.8396,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.9328,0.0874,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.8531,0.1058,0.0256,0.0013</t>
-  </si>
-  <si>
-    <t>0.7626,0.0025,0.4530,0.0006</t>
-  </si>
-  <si>
-    <t>0.8922,0.0638,0.0271,0.0008</t>
-  </si>
-  <si>
-    <t>0.9272,0.0620,0.0066,0.0001</t>
-  </si>
-  <si>
-    <t>0.8605,0.0790,0.0518,0.0059</t>
-  </si>
-  <si>
-    <t>0.9517,0.0825,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8203,0.1839,0.0087,0.0001</t>
-  </si>
-  <si>
-    <t>0.9221,0.0723,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.0295,0.1662,0.8866,0.0004</t>
-  </si>
-  <si>
-    <t>0.9700,0.0306,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.6062,0.4641,0.0078,0.0012</t>
-  </si>
-  <si>
-    <t>0.7981,0.2519,0.0087,0.0010</t>
-  </si>
-  <si>
-    <t>0.9804,0.0141,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9672,0.0318,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9438,0.0444,0.0035,0.0014</t>
-  </si>
-  <si>
-    <t>0.8596,0.0984,0.0065,0.0044</t>
-  </si>
-  <si>
-    <t>0.8548,0.1969,0.0061,0.0011</t>
-  </si>
-  <si>
-    <t>0.9527,0.0535,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.6800,0.3237,0.0252,0.0022</t>
-  </si>
-  <si>
-    <t>0.7948,0.2101,0.0173,0.0039</t>
-  </si>
-  <si>
-    <t>0.9573,0.0013,0.0985,0.0001</t>
-  </si>
-  <si>
-    <t>0.6590,0.1431,0.1096,0.0007</t>
-  </si>
-  <si>
-    <t>0.7249,0.0044,0.4713,0.0012</t>
-  </si>
-  <si>
-    <t>0.9681,0.0035,0.0379,0.0002</t>
-  </si>
-  <si>
-    <t>0.9474,0.0262,0.0121,0.0011</t>
-  </si>
-  <si>
-    <t>0.9595,0.0369,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.9305,0.0291,0.0280,0.0012</t>
-  </si>
-  <si>
-    <t>0.9246,0.0571,0.0093,0.0008</t>
-  </si>
-  <si>
-    <t>0.9652,0.0070,0.0028,0.0048</t>
-  </si>
-  <si>
-    <t>0.8397,0.0494,0.0550,0.0340</t>
-  </si>
-  <si>
-    <t>0.9531,0.0179,0.0095,0.0034</t>
-  </si>
-  <si>
-    <t>0.9628,0.0064,0.0034,0.0104</t>
-  </si>
-  <si>
-    <t>0.1721,0.7157,0.0630,0.0003</t>
-  </si>
-  <si>
-    <t>0.9248,0.0647,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.9066,0.0827,0.0168,0.0018</t>
-  </si>
-  <si>
-    <t>0.8453,0.1976,0.0094,0.0018</t>
-  </si>
-  <si>
-    <t>0.9624,0.0378,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.8159,0.2256,0.0066,0.0019</t>
-  </si>
-  <si>
-    <t>0.9033,0.0685,0.0058,0.0012</t>
-  </si>
-  <si>
-    <t>0.5669,0.4475,0.0058,0.0020</t>
-  </si>
-  <si>
-    <t>0.4270,0.1475,0.6299,0.0226</t>
-  </si>
-  <si>
-    <t>0.9458,0.0341,0.0082,0.0012</t>
-  </si>
-  <si>
-    <t>0.9604,0.0208,0.0025,0.0015</t>
-  </si>
-  <si>
-    <t>0.9507,0.0259,0.0092,0.0013</t>
-  </si>
-  <si>
-    <t>0.9200,0.0677,0.0074,0.0006</t>
-  </si>
-  <si>
-    <t>0.9045,0.1249,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.9513,0.0401,0.0054,0.0006</t>
-  </si>
-  <si>
-    <t>0.9098,0.1176,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.8987,0.1388,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.9578,0.0324,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.9231,0.0648,0.0026,0.0022</t>
-  </si>
-  <si>
-    <t>0.9328,0.0836,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9147,0.0752,0.0045,0.0019</t>
-  </si>
-  <si>
-    <t>0.9694,0.0185,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.8792,0.1367,0.0053,0.0013</t>
-  </si>
-  <si>
-    <t>0.9639,0.0294,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.8203,0.1924,0.0028,0.0017</t>
-  </si>
-  <si>
-    <t>0.8979,0.1079,0.0015,0.0011</t>
-  </si>
-  <si>
-    <t>0.6449,0.5459,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.9798,0.0161,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.4850,0.4456,0.1264,0.0017</t>
-  </si>
-  <si>
-    <t>0.9107,0.0878,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.7008,0.4239,0.0121,0.0011</t>
-  </si>
-  <si>
-    <t>0.9701,0.0408,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.5111,0.6316,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.0254,0.5715,0.8242,0.0004</t>
-  </si>
-  <si>
-    <t>0.9063,0.1047,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.4410,0.0064,0.7076,0.0026</t>
-  </si>
-  <si>
-    <t>0.9846,0.0011,0.0260,0.0001</t>
-  </si>
-  <si>
-    <t>0.6611,0.0483,0.3254,0.0041</t>
-  </si>
-  <si>
-    <t>0.5284,0.0090,0.5918,0.0005</t>
-  </si>
-  <si>
-    <t>0.9703,0.0014,0.0560,0.0003</t>
-  </si>
-  <si>
-    <t>0.4833,0.0066,0.6764,0.0008</t>
-  </si>
-  <si>
-    <t>0.4904,0.0063,0.7296,0.0007</t>
-  </si>
-  <si>
-    <t>0.9533,0.0341,0.0081,0.0002</t>
-  </si>
-  <si>
-    <t>0.9698,0.0165,0.0084,0.0003</t>
-  </si>
-  <si>
-    <t>0.9437,0.0240,0.0242,0.0008</t>
-  </si>
-  <si>
-    <t>0.7928,0.2603,0.0070,0.0002</t>
-  </si>
-  <si>
-    <t>0.9526,0.0361,0.0062,0.0001</t>
-  </si>
-  <si>
-    <t>0.9133,0.0520,0.0152,0.0002</t>
-  </si>
-  <si>
-    <t>0.8614,0.0616,0.0632,0.0018</t>
-  </si>
-  <si>
-    <t>0.9675,0.0110,0.0102,0.0006</t>
-  </si>
-  <si>
-    <t>0.3788,0.7920,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.7328,0.3731,0.0063,0.0014</t>
-  </si>
-  <si>
-    <t>0.5579,0.5881,0.0070,0.0009</t>
-  </si>
-  <si>
-    <t>0.9713,0.0328,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.5183,0.6724,0.0055,0.0004</t>
-  </si>
-  <si>
-    <t>0.9144,0.0404,0.0223,0.0015</t>
-  </si>
-  <si>
-    <t>0.9276,0.0519,0.0134,0.0005</t>
-  </si>
-  <si>
-    <t>0.9610,0.0086,0.0231,0.0023</t>
-  </si>
-  <si>
-    <t>0.9495,0.0130,0.0463,0.0007</t>
-  </si>
-  <si>
-    <t>0.8725,0.0288,0.1189,0.0054</t>
-  </si>
-  <si>
-    <t>0.3588,0.0140,0.6932,0.0052</t>
-  </si>
-  <si>
-    <t>0.7448,0.0040,0.3595,0.0002</t>
-  </si>
-  <si>
-    <t>0.9943,0.0005,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.9465,0.0012,0.0895,0.0010</t>
-  </si>
-  <si>
-    <t>0.9175,0.0335,0.0229,0.0003</t>
-  </si>
-  <si>
-    <t>0.8237,0.1606,0.0063,0.0025</t>
-  </si>
-  <si>
-    <t>0.9268,0.0733,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.8514,0.1999,0.0051,0.0011</t>
-  </si>
-  <si>
-    <t>0.9657,0.0322,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.7205,0.2214,0.0060,0.0045</t>
-  </si>
-  <si>
-    <t>0.8902,0.1261,0.0021,0.0010</t>
-  </si>
-  <si>
-    <t>0.7130,0.3846,0.0084,0.0025</t>
-  </si>
-  <si>
-    <t>0.7375,0.3490,0.0043,0.0008</t>
-  </si>
-  <si>
-    <t>0.9132,0.0460,0.0447,0.0017</t>
-  </si>
-  <si>
-    <t>0.8659,0.1072,0.0339,0.0009</t>
-  </si>
-  <si>
-    <t>0.5346,0.5021,0.0546,0.0038</t>
-  </si>
-  <si>
-    <t>0.9254,0.0027,0.1180,0.0002</t>
-  </si>
-  <si>
-    <t>0.0658,0.0091,0.9539,0.0009</t>
-  </si>
-  <si>
-    <t>0.9178,0.0180,0.0743,0.0011</t>
-  </si>
-  <si>
-    <t>0.0104,0.0044,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.8343,0.0160,0.1904,0.0007</t>
-  </si>
-  <si>
-    <t>0.0525,0.0343,0.9380,0.0048</t>
-  </si>
-  <si>
-    <t>0.9491,0.0018,0.1123,0.0002</t>
-  </si>
-  <si>
-    <t>0.3300,0.4437,0.2920,0.0054</t>
-  </si>
-  <si>
-    <t>0.9444,0.0416,0.0091,0.0004</t>
-  </si>
-  <si>
-    <t>0.9579,0.0068,0.0472,0.0007</t>
-  </si>
-  <si>
-    <t>0.9852,0.0027,0.0080,0.0006</t>
-  </si>
-  <si>
-    <t>0.8323,0.2176,0.0047,0.0013</t>
-  </si>
-  <si>
-    <t>0.9564,0.0310,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.7569,0.2855,0.0126,0.0028</t>
-  </si>
-  <si>
-    <t>0.8816,0.1109,0.0023,0.0013</t>
-  </si>
-  <si>
-    <t>0.9507,0.0327,0.0006,0.0010</t>
-  </si>
-  <si>
-    <t>0.9173,0.1172,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.8173,0.2301,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.7394,0.3242,0.0050,0.0012</t>
-  </si>
-  <si>
-    <t>0.9149,0.0063,0.1287,0.0004</t>
-  </si>
-  <si>
-    <t>0.8246,0.0046,0.3193,0.0003</t>
-  </si>
-  <si>
-    <t>0.7089,0.0178,0.3591,0.0036</t>
-  </si>
-  <si>
-    <t>0.6210,0.0219,0.3878,0.0011</t>
-  </si>
-  <si>
-    <t>0.7428,0.0017,0.4641,0.0001</t>
-  </si>
-  <si>
-    <t>0.9679,0.0043,0.0254,0.0010</t>
-  </si>
-  <si>
-    <t>0.9795,0.0037,0.0171,0.0002</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0047,0.0000</t>
-  </si>
-  <si>
-    <t>0.9582,0.0367,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9124,0.0143,0.0581,0.0098</t>
-  </si>
-  <si>
-    <t>0.9596,0.0134,0.0055,0.0027</t>
-  </si>
-  <si>
-    <t>0.9774,0.0028,0.0032,0.0049</t>
-  </si>
-  <si>
-    <t>0.9669,0.0047,0.0030,0.0154</t>
-  </si>
-  <si>
-    <t>0.9354,0.0512,0.0059,0.0004</t>
+    <t>0.9465,0.0063,0.0145,0.0174</t>
+  </si>
+  <si>
+    <t>0.0165,0.0017,0.0001,0.9938</t>
+  </si>
+  <si>
+    <t>0.9533,0.0021,0.0004,0.0331</t>
+  </si>
+  <si>
+    <t>0.0862,0.0044,0.0004,0.9660</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9959,0.0013,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0019,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9961,0.0005,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9971,0.0010,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0030,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.8794,0.0169,0.1256,0.0012</t>
+  </si>
+  <si>
+    <t>0.0780,0.0064,0.9259,0.0085</t>
+  </si>
+  <si>
+    <t>0.8616,0.0010,0.2947,0.0001</t>
+  </si>
+  <si>
+    <t>0.0243,0.0064,0.9701,0.0035</t>
+  </si>
+  <si>
+    <t>0.9696,0.0082,0.0122,0.0028</t>
+  </si>
+  <si>
+    <t>0.0006,0.9983,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0097,0.9773,0.0064,0.0232</t>
+  </si>
+  <si>
+    <t>0.1336,0.8948,0.0245,0.0023</t>
+  </si>
+  <si>
+    <t>0.0147,0.9767,0.0057,0.0091</t>
+  </si>
+  <si>
+    <t>0.0020,0.9964,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.8487,0.0031,0.2862,0.0019</t>
+  </si>
+  <si>
+    <t>0.9215,0.0024,0.1301,0.0010</t>
+  </si>
+  <si>
+    <t>0.0049,0.0006,0.9920,0.0013</t>
+  </si>
+  <si>
+    <t>0.3765,0.0025,0.7438,0.0017</t>
+  </si>
+  <si>
+    <t>0.0334,0.0022,0.9754,0.0017</t>
+  </si>
+  <si>
+    <t>0.0179,0.0017,0.9773,0.0028</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.7235,0.4148,0.0042,0.0044</t>
+  </si>
+  <si>
+    <t>0.1221,0.3774,0.6470,0.0053</t>
+  </si>
+  <si>
+    <t>0.0025,0.0075,0.9944,0.0023</t>
+  </si>
+  <si>
+    <t>0.0033,0.9813,0.0178,0.0000</t>
+  </si>
+  <si>
+    <t>0.8508,0.0702,0.0512,0.0324</t>
+  </si>
+  <si>
+    <t>0.8687,0.0659,0.0766,0.0031</t>
+  </si>
+  <si>
+    <t>0.7306,0.3805,0.0094,0.0008</t>
+  </si>
+  <si>
+    <t>0.0092,0.9796,0.0352,0.0009</t>
+  </si>
+  <si>
+    <t>0.0179,0.0141,0.9549,0.0158</t>
+  </si>
+  <si>
+    <t>0.0177,0.0025,0.9831,0.0018</t>
+  </si>
+  <si>
+    <t>0.0067,0.0033,0.9918,0.0006</t>
+  </si>
+  <si>
+    <t>0.0269,0.0007,0.9676,0.0055</t>
+  </si>
+  <si>
+    <t>0.0385,0.0360,0.9702,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.9906,0.0031,0.0019</t>
+  </si>
+  <si>
+    <t>0.0127,0.0099,0.9814,0.0006</t>
+  </si>
+  <si>
+    <t>0.1982,0.1419,0.0228,0.7910</t>
+  </si>
+  <si>
+    <t>0.0020,0.9898,0.0044,0.0095</t>
+  </si>
+  <si>
+    <t>0.0038,0.9860,0.0099,0.0032</t>
+  </si>
+  <si>
+    <t>0.0006,0.9962,0.0041,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.0405,0.9866,0.0153</t>
+  </si>
+  <si>
+    <t>0.0006,0.0105,0.9958,0.0013</t>
+  </si>
+  <si>
+    <t>0.0043,0.0009,0.9920,0.0018</t>
+  </si>
+  <si>
+    <t>0.0618,0.0014,0.9576,0.0014</t>
+  </si>
+  <si>
+    <t>0.0027,0.0034,0.9927,0.0012</t>
+  </si>
+  <si>
+    <t>0.0036,0.0072,0.9924,0.0010</t>
+  </si>
+  <si>
+    <t>0.9591,0.0486,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9776,0.0066,0.0118,0.0024</t>
+  </si>
+  <si>
+    <t>0.9833,0.0114,0.0041,0.0012</t>
+  </si>
+  <si>
+    <t>0.0114,0.0053,0.9899,0.0013</t>
+  </si>
+  <si>
+    <t>0.9895,0.0020,0.0050,0.0022</t>
+  </si>
+  <si>
+    <t>0.9943,0.0026,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9647,0.0482,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.0006,0.9411,0.9917,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.0015,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.0046,0.0465,0.9823,0.0142</t>
+  </si>
+  <si>
+    <t>0.0006,0.9865,0.8596,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.0070,0.9939,0.0013</t>
+  </si>
+  <si>
+    <t>0.1798,0.8499,0.0179,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.9982,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9462,0.0067,0.0714,0.0025</t>
+  </si>
+  <si>
+    <t>0.7611,0.1000,0.1250,0.0043</t>
+  </si>
+  <si>
+    <t>0.0072,0.0195,0.9809,0.0192</t>
+  </si>
+  <si>
+    <t>0.0005,0.9681,0.9803,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.9488,0.7385,0.0014</t>
+  </si>
+  <si>
+    <t>0.0017,0.9905,0.1610,0.0012</t>
+  </si>
+  <si>
+    <t>0.0064,0.9658,0.4660,0.0012</t>
+  </si>
+  <si>
+    <t>0.0051,0.0002,0.0013,0.9963</t>
+  </si>
+  <si>
+    <t>0.0005,0.0010,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0009,0.0068,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.0029,0.0003,0.0018,0.9974</t>
+  </si>
+  <si>
+    <t>0.0037,0.0006,0.0016,0.9970</t>
+  </si>
+  <si>
+    <t>0.0017,0.0011,0.0020,0.9975</t>
+  </si>
+  <si>
+    <t>0.0006,0.9852,0.8885,0.0014</t>
+  </si>
+  <si>
+    <t>0.0030,0.6484,0.9842,0.0008</t>
+  </si>
+  <si>
+    <t>0.0181,0.4444,0.7957,0.0027</t>
+  </si>
+  <si>
+    <t>0.0005,0.4466,0.9966,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9955,0.9636,0.0000</t>
+  </si>
+  <si>
+    <t>0.0082,0.9693,0.0990,0.0030</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0024,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9500,0.0600,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.9923,0.0027,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9912,0.0036,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9954,0.0016,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9954,0.0010,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9925,0.0047,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9951,0.0018,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0049,0.0031,0.9931,0.0013</t>
+  </si>
+  <si>
+    <t>0.0115,0.0031,0.9896,0.0010</t>
+  </si>
+  <si>
+    <t>0.9451,0.0050,0.0320,0.0107</t>
+  </si>
+  <si>
+    <t>0.0223,0.0006,0.9831,0.0009</t>
+  </si>
+  <si>
+    <t>0.0024,0.9965,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.9979,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0142,0.9828,0.0011,0.0023</t>
+  </si>
+  <si>
+    <t>0.0172,0.9755,0.0029,0.0045</t>
+  </si>
+  <si>
+    <t>0.0025,0.9962,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0028,0.9948,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.4840,0.7457,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.6430,0.0364,0.3687,0.0143</t>
+  </si>
+  <si>
+    <t>0.1660,0.0025,0.8780,0.0033</t>
+  </si>
+  <si>
+    <t>0.5190,0.0455,0.4397,0.0281</t>
+  </si>
+  <si>
+    <t>0.2482,0.0149,0.8232,0.0055</t>
+  </si>
+  <si>
+    <t>0.0202,0.0687,0.0311,0.9567</t>
+  </si>
+  <si>
+    <t>0.0008,0.9980,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.9961,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.0052,0.9838,0.0080,0.0046</t>
+  </si>
+  <si>
+    <t>0.0021,0.7749,0.9287,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.9949,0.0073,0.0002</t>
+  </si>
+  <si>
+    <t>0.7552,0.3285,0.0103,0.0020</t>
+  </si>
+  <si>
+    <t>0.8141,0.2442,0.0101,0.0009</t>
+  </si>
+  <si>
+    <t>0.9899,0.0023,0.0023,0.0035</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9805,0.0040,0.0127,0.0024</t>
+  </si>
+  <si>
+    <t>0.9901,0.0042,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9931,0.0006,0.0009,0.0042</t>
+  </si>
+  <si>
+    <t>0.9927,0.0011,0.0068,0.0004</t>
+  </si>
+  <si>
+    <t>0.9769,0.0057,0.0072,0.0069</t>
+  </si>
+  <si>
+    <t>0.9919,0.0029,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.0059,0.1061,0.9637,0.0045</t>
+  </si>
+  <si>
+    <t>0.0006,0.2765,0.9924,0.0004</t>
+  </si>
+  <si>
+    <t>0.0017,0.0080,0.9928,0.0013</t>
+  </si>
+  <si>
+    <t>0.2185,0.0133,0.8755,0.0044</t>
+  </si>
+  <si>
+    <t>0.9781,0.0026,0.0117,0.0027</t>
+  </si>
+  <si>
+    <t>0.8212,0.0062,0.1655,0.0137</t>
+  </si>
+  <si>
+    <t>0.1989,0.0017,0.8330,0.0040</t>
+  </si>
+  <si>
+    <t>0.8173,0.0330,0.1703,0.0072</t>
+  </si>
+  <si>
+    <t>0.0083,0.0003,0.0004,0.9967</t>
+  </si>
+  <si>
+    <t>0.0002,0.0026,0.0016,0.9990</t>
+  </si>
+  <si>
+    <t>0.0005,0.0031,0.0025,0.9986</t>
+  </si>
+  <si>
+    <t>0.0115,0.0004,0.0021,0.9932</t>
+  </si>
+  <si>
+    <t>0.0022,0.9605,0.2391,0.0074</t>
+  </si>
+  <si>
+    <t>0.9941,0.0006,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.0427,0.9525,0.0037,0.0078</t>
+  </si>
+  <si>
+    <t>0.9835,0.0028,0.0061,0.0054</t>
+  </si>
+  <si>
+    <t>0.1459,0.8879,0.0091,0.0022</t>
+  </si>
+  <si>
+    <t>0.9893,0.0005,0.0008,0.0052</t>
+  </si>
+  <si>
+    <t>0.8424,0.0009,0.0022,0.2509</t>
+  </si>
+  <si>
+    <t>0.9839,0.0019,0.0089,0.0023</t>
+  </si>
+  <si>
+    <t>0.0081,0.0434,0.9214,0.2350</t>
+  </si>
+  <si>
+    <t>0.8149,0.0005,0.0012,0.3716</t>
+  </si>
+  <si>
+    <t>0.9784,0.0019,0.0016,0.0110</t>
+  </si>
+  <si>
+    <t>0.7601,0.2966,0.0064,0.0124</t>
+  </si>
+  <si>
+    <t>0.9849,0.0034,0.0041,0.0016</t>
+  </si>
+  <si>
+    <t>0.9586,0.0280,0.0083,0.0041</t>
+  </si>
+  <si>
+    <t>0.7073,0.2149,0.0374,0.0119</t>
+  </si>
+  <si>
+    <t>0.9591,0.0145,0.0235,0.0012</t>
+  </si>
+  <si>
+    <t>0.9614,0.0313,0.0063,0.0038</t>
+  </si>
+  <si>
+    <t>0.9953,0.0010,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9933,0.0012,0.0008,0.0020</t>
+  </si>
+  <si>
+    <t>0.9909,0.0014,0.0026,0.0047</t>
+  </si>
+  <si>
+    <t>0.9906,0.0010,0.0009,0.0039</t>
+  </si>
+  <si>
+    <t>0.9910,0.0022,0.0014,0.0020</t>
+  </si>
+  <si>
+    <t>0.9742,0.0028,0.0055,0.0121</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.8828,0.1231,0.0046,0.0053</t>
+  </si>
+  <si>
+    <t>0.8455,0.1999,0.0055,0.0006</t>
+  </si>
+  <si>
+    <t>0.9564,0.0573,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.7409,0.2559,0.0523,0.0116</t>
+  </si>
+  <si>
+    <t>0.9902,0.0029,0.0004,0.0025</t>
+  </si>
+  <si>
+    <t>0.9178,0.0364,0.0162,0.0172</t>
+  </si>
+  <si>
+    <t>0.9963,0.0009,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.8125,0.1406,0.0008,0.0138</t>
+  </si>
+  <si>
+    <t>0.0020,0.0147,0.9969,0.0006</t>
+  </si>
+  <si>
+    <t>0.9811,0.0088,0.0050,0.0013</t>
+  </si>
+  <si>
+    <t>0.0020,0.0011,0.9960,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.1370,0.9919,0.0125</t>
+  </si>
+  <si>
+    <t>0.0476,0.0065,0.9364,0.0092</t>
+  </si>
+  <si>
+    <t>0.0069,0.0260,0.9872,0.0047</t>
+  </si>
+  <si>
+    <t>0.0237,0.0092,0.9754,0.0018</t>
+  </si>
+  <si>
+    <t>0.0019,0.0004,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.0050,0.9930,0.0018</t>
+  </si>
+  <si>
+    <t>0.0945,0.0217,0.8530,0.0247</t>
+  </si>
+  <si>
+    <t>0.3149,0.0068,0.7992,0.0020</t>
+  </si>
+  <si>
+    <t>0.0169,0.0124,0.9776,0.0017</t>
+  </si>
+  <si>
+    <t>0.2764,0.0314,0.7141,0.0022</t>
+  </si>
+  <si>
+    <t>0.0267,0.7200,0.4231,0.0069</t>
+  </si>
+  <si>
+    <t>0.8169,0.0100,0.2155,0.0007</t>
+  </si>
+  <si>
+    <t>0.3920,0.0290,0.6221,0.0359</t>
+  </si>
+  <si>
+    <t>0.1866,0.0233,0.8054,0.0020</t>
+  </si>
+  <si>
+    <t>0.0400,0.9720,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.1248,0.9308,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.0093,0.9852,0.0004,0.0105</t>
+  </si>
+  <si>
+    <t>0.9133,0.0929,0.0097,0.0043</t>
+  </si>
+  <si>
+    <t>0.2376,0.8815,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.8407,0.1001,0.0385,0.0042</t>
+  </si>
+  <si>
+    <t>0.9019,0.0031,0.1439,0.0031</t>
+  </si>
+  <si>
+    <t>0.8030,0.0345,0.1217,0.0448</t>
+  </si>
+  <si>
+    <t>0.7218,0.0341,0.2823,0.0259</t>
+  </si>
+  <si>
+    <t>0.6471,0.0025,0.1544,0.0580</t>
+  </si>
+  <si>
+    <t>0.0028,0.0024,0.9923,0.0046</t>
+  </si>
+  <si>
+    <t>0.0582,0.0313,0.9079,0.0094</t>
+  </si>
+  <si>
+    <t>0.0610,0.0563,0.9031,0.0097</t>
+  </si>
+  <si>
+    <t>0.0108,0.0065,0.9860,0.0008</t>
+  </si>
+  <si>
+    <t>0.0669,0.0167,0.9016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9904,0.0031,0.0005,0.0021</t>
+  </si>
+  <si>
+    <t>0.9924,0.0036,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9787,0.0153,0.0039,0.0021</t>
+  </si>
+  <si>
+    <t>0.9900,0.0073,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9347,0.0857,0.0020,0.0026</t>
+  </si>
+  <si>
+    <t>0.9877,0.0040,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.9920,0.0052,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.9945,0.0021,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.0015,0.0098,0.9975,0.0007</t>
+  </si>
+  <si>
+    <t>0.0094,0.9587,0.1363,0.0032</t>
+  </si>
+  <si>
+    <t>0.9239,0.0047,0.0552,0.0052</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0035,0.9948,0.0054</t>
+  </si>
+  <si>
+    <t>0.0003,0.0072,0.9983,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0013,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0044,0.9882,0.0021</t>
+  </si>
+  <si>
+    <t>0.0008,0.0038,0.9981,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.0389,0.9865,0.0026</t>
+  </si>
+  <si>
+    <t>0.0750,0.0316,0.8707,0.0165</t>
+  </si>
+  <si>
+    <t>0.9423,0.0025,0.0966,0.0010</t>
+  </si>
+  <si>
+    <t>0.3536,0.0009,0.5638,0.0207</t>
+  </si>
+  <si>
+    <t>0.9292,0.0052,0.0944,0.0023</t>
+  </si>
+  <si>
+    <t>0.9955,0.0022,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9799,0.0139,0.0035,0.0013</t>
+  </si>
+  <si>
+    <t>0.9979,0.0004,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9912,0.0057,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9957,0.0005,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9901,0.0025,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9917,0.0022,0.0010,0.0021</t>
+  </si>
+  <si>
+    <t>0.0021,0.0022,0.9955,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0667,0.9949,0.0011</t>
+  </si>
+  <si>
+    <t>0.0013,0.0062,0.9922,0.0062</t>
+  </si>
+  <si>
+    <t>0.0226,0.0124,0.9731,0.0030</t>
+  </si>
+  <si>
+    <t>0.0094,0.0008,0.9928,0.0003</t>
+  </si>
+  <si>
+    <t>0.0192,0.0078,0.9300,0.0781</t>
+  </si>
+  <si>
+    <t>0.2990,0.0110,0.7398,0.0086</t>
+  </si>
+  <si>
+    <t>0.0177,0.0060,0.9764,0.0038</t>
+  </si>
+  <si>
+    <t>0.4181,0.0004,0.0060,0.6586</t>
+  </si>
+  <si>
+    <t>0.0135,0.0054,0.0018,0.9920</t>
+  </si>
+  <si>
+    <t>0.1205,0.0010,0.0002,0.9695</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.0009,0.9990</t>
+  </si>
+  <si>
+    <t>0.0054,0.0053,0.0018,0.9953</t>
+  </si>
+  <si>
+    <t>0.9883,0.0006,0.0046,0.0024</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D223" t="s">
         <v>485</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
